--- a/sheets/대금율보/검수/날개.xlsx
+++ b/sheets/대금율보/검수/날개.xlsx
@@ -4203,30 +4203,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="114.74" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="114.74" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="114.74" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="114.74" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="114.74" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="114.74" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="114.74" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4634,7 +4634,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="114.74" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="114.74" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="114.74" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="114.74" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="114.74" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="114.74" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="114.74" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="114.74" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="114.74" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5137,6 +5137,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>